--- a/intake_forms/032_quilt_intake_form--intake_forms.xlsx
+++ b/intake_forms/032_quilt_intake_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -914,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1134,29 +1134,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>tapestries</t>
+          <t>bed_quilts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tapestries</t>
+          <t>Bed Quilts</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>material_type_choices</t>
+          <t>thread_color_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bed_quilts</t>
+          <t>color_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bed Quilts</t>
+          <t>Color 1</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>color_1</t>
+          <t>color_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Color 1</t>
+          <t>Color 2</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>color_2</t>
+          <t>color_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Color 2</t>
+          <t>Color 3</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>color_3</t>
+          <t>color_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Color 3</t>
+          <t>Color 4</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>color_4</t>
+          <t>color_5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Color 4</t>
+          <t>Color 5</t>
         </is>
       </c>
     </row>
@@ -1236,29 +1236,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>color_5</t>
+          <t>color_6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Color 5</t>
+          <t>Color 6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>thread_color_choices</t>
+          <t>custom_quilts_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>color_6</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Color 6</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1270,29 +1270,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>custom_quilts_choices</t>
+          <t>design_type_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Hand</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Machine</t>
         </is>
       </c>
     </row>
@@ -1321,29 +1321,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Machine</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>design_type_choices</t>
+          <t>customer_phone_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1372,27 +1372,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>customer_phone_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
